--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="680">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -1416,6 +1416,12 @@
   </si>
   <si>
     <t>Matr_008</t>
+  </si>
+  <si>
+    <t>323111</t>
+  </si>
+  <si>
+    <t>Matr_022</t>
   </si>
   <si>
     <t>329999</t>
@@ -2104,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C339"/>
+  <dimension ref="A1:C340"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -4823,6 +4829,14 @@
         <v>677</v>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Mapping_casi_uso/3_dec_use_case.xlsx
+++ b/docs/Mapping_casi_uso/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="702">
   <si>
     <t>ID USECASE</t>
   </si>
@@ -1968,6 +1968,12 @@
   </si>
   <si>
     <t>Citt_046</t>
+  </si>
+  <si>
+    <t>52155</t>
+  </si>
+  <si>
+    <t>Citt_050</t>
   </si>
   <si>
     <t>52211</t>
@@ -2170,7 +2176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.68359375" customWidth="true" bestFit="true"/>
@@ -4977,6 +4983,14 @@
         <v>699</v>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
